--- a/StructureDefinition-access-report-data-out.xlsx
+++ b/StructureDefinition-access-report-data-out.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:45:33-04:00</t>
+    <t>2026-05-18T15:59:44-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -529,7 +529,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSReportDataResultVS|0.9.6</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSReportDataResultVS|0.9.8</t>
   </si>
   <si>
     <t>Parameters.parameter:result.resource</t>

--- a/StructureDefinition-access-report-data-out.xlsx
+++ b/StructureDefinition-access-report-data-out.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T15:59:44-04:00</t>
+    <t>2026-05-20T09:30:43-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-access-report-data-out.xlsx
+++ b/StructureDefinition-access-report-data-out.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.8</t>
+    <t>0.9.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T09:30:43-04:00</t>
+    <t>2026-06-04T22:54:52-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -529,7 +529,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSReportDataResultVS|0.9.8</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSReportDataResultVS|0.9.11</t>
   </si>
   <si>
     <t>Parameters.parameter:result.resource</t>
@@ -880,7 +880,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="70.71875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.71875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="16.2578125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-access-report-data-out.xlsx
+++ b/StructureDefinition-access-report-data-out.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T22:54:52-04:00</t>
+    <t>2026-06-04T23:05:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-access-report-data-out.xlsx
+++ b/StructureDefinition-access-report-data-out.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.11</t>
+    <t>0.9.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T23:05:21-04:00</t>
+    <t>2026-06-10T23:08:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -529,7 +529,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSReportDataResultVS|0.9.11</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSReportDataResultVS|0.9.12</t>
   </si>
   <si>
     <t>Parameters.parameter:result.resource</t>
